--- a/Интеллектуальный анализ данных/Лабораторные работы/ЛР3/ExpData.xlsx
+++ b/Интеллектуальный анализ данных/Лабораторные работы/ЛР3/ExpData.xlsx
@@ -8,26 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Honor\OneDrive\Рабочий стол\Lessons\6-semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5547C9B9-94C6-4757-BD2B-DBBFB6822D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA14556-FA0C-4C0C-9007-D7767F67EE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1824" yWindow="2484" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
     <sheet name="Страны_СредняяЗП" sheetId="2" r:id="rId2"/>
     <sheet name="Страны_СредняяЗП_в_Колонку" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист1" sheetId="4" r:id="rId4"/>
+    <sheet name="Лист6" sheetId="9" r:id="rId5"/>
+    <sheet name="1" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="326">
   <si>
     <t>Страна</t>
   </si>
@@ -942,13 +954,76 @@
   </si>
   <si>
     <t>33.4475</t>
+  </si>
+  <si>
+    <t>До 15</t>
+  </si>
+  <si>
+    <t>До 45</t>
+  </si>
+  <si>
+    <t>От 45</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>Среднее</t>
+  </si>
+  <si>
+    <t>Однофакторный дисперсионный анализ</t>
+  </si>
+  <si>
+    <t>ИТОГИ</t>
+  </si>
+  <si>
+    <t>Группы</t>
+  </si>
+  <si>
+    <t>Счет</t>
+  </si>
+  <si>
+    <t>Дисперсия</t>
+  </si>
+  <si>
+    <t>Дисперсионный анализ</t>
+  </si>
+  <si>
+    <t>Источник вариации</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>P-Значение</t>
+  </si>
+  <si>
+    <t>F критическое</t>
+  </si>
+  <si>
+    <t>Между группами</t>
+  </si>
+  <si>
+    <t>Внутри групп</t>
+  </si>
+  <si>
+    <t>Итого</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -972,6 +1047,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -986,7 +1075,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1020,13 +1109,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1045,13 +1163,51 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Вывод" xfId="1" builtinId="21"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{A36A347A-F292-4748-875D-9062A2E8BF18}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1348,7 +1504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -1359,7 +1515,7 @@
     <col min="6" max="6" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1381,8 +1537,17 @@
       <c r="G1" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I1" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
@@ -1404,8 +1569,27 @@
       <c r="G2" s="5">
         <v>47.668300000000002</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <f>IF(G2 &lt; 15,D2, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>IF(AND(G2 &lt; 45, G2&gt;15),D2, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>IF(G2&gt;45,D2, 0)</f>
+        <v>61.06</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ref="M2:M65" si="0">IF(J2&lt;&gt;0,$J$1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -1427,8 +1611,27 @@
       <c r="G3" s="5">
         <v>42.214599999999997</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="1">IF(G3 &lt; 15,D3, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>IF(AND(G3 &lt; 45, G3&gt;15),D3, 0)</f>
+        <v>73.319999999999993</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="2">IF(G3&gt;45,D3, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N3">
+        <v>73.319999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1450,8 +1653,27 @@
       <c r="G4" s="5">
         <v>22.1432</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J67" si="3">IF(AND(G4 &lt; 45, G4&gt;15),D4, 0)</f>
+        <v>56.74</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N4">
+        <v>56.74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1473,8 +1695,27 @@
       <c r="G5" s="5">
         <v>24.020399999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="3"/>
+        <v>64.510000000000005</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M5" t="str">
+        <f>IF(J5&lt;&gt;0,$J$1,0)</f>
+        <v>До 45</v>
+      </c>
+      <c r="N5">
+        <v>64.510000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>56</v>
       </c>
@@ -1496,8 +1737,27 @@
       <c r="G6" s="5">
         <v>44.591700000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>72.05</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N6">
+        <v>72.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>34</v>
       </c>
@@ -1519,8 +1779,27 @@
       <c r="G7" s="5">
         <v>14.273099999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>44.53</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>41</v>
       </c>
@@ -1542,8 +1821,27 @@
       <c r="G8" s="5">
         <v>11.8727</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>50.57</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>51</v>
       </c>
@@ -1565,8 +1863,27 @@
       <c r="G9" s="5">
         <v>38.947499999999998</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>54.28</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N9">
+        <v>54.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>76</v>
       </c>
@@ -1588,8 +1905,27 @@
       <c r="G10" s="5">
         <v>4.6841999999999997</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>26.94</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>73</v>
       </c>
@@ -1611,8 +1947,27 @@
       <c r="G11" s="5">
         <v>17.5046</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>54.67</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N11">
+        <v>54.67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>67</v>
       </c>
@@ -1634,8 +1989,27 @@
       <c r="G12" s="5">
         <v>18.9941</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>60.22</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N12">
+        <v>60.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>64</v>
       </c>
@@ -1657,8 +2031,27 @@
       <c r="G13" s="5">
         <v>125.4355</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>63.78</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
@@ -1680,8 +2073,27 @@
       <c r="G14" s="5">
         <v>16.008900000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>62.41</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N14">
+        <v>62.41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>72</v>
       </c>
@@ -1703,8 +2115,27 @@
       <c r="G15" s="5">
         <v>10.260300000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>61.54</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
@@ -1726,8 +2157,27 @@
       <c r="G16" s="5">
         <v>61.3264</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>59.03</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>65</v>
       </c>
@@ -1749,8 +2199,27 @@
       <c r="G17" s="5">
         <v>4.3868</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" si="1"/>
+        <v>34.47</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>69</v>
       </c>
@@ -1772,8 +2241,27 @@
       <c r="G18" s="5">
         <v>4.2523</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="1"/>
+        <v>36.4</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1795,8 +2283,27 @@
       <c r="G19" s="5">
         <v>15.1922</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>51.44</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N19">
+        <v>51.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>63</v>
       </c>
@@ -1818,8 +2325,27 @@
       <c r="G20" s="5">
         <v>3.8130999999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>32.68</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -1841,8 +2367,27 @@
       <c r="G21" s="5">
         <v>4.6158000000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="1"/>
+        <v>42.66</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>26</v>
       </c>
@@ -1864,8 +2409,27 @@
       <c r="G22" s="5">
         <v>6.8696999999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="1"/>
+        <v>47.68</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
@@ -1887,8 +2451,27 @@
       <c r="G23" s="5">
         <v>1.6366000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>43.39</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>6</v>
       </c>
@@ -1910,8 +2493,27 @@
       <c r="G24" s="5">
         <v>5.1379999999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>49.76</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
@@ -1933,8 +2535,27 @@
       <c r="G25" s="5">
         <v>5.7367999999999997</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <f t="shared" si="1"/>
+        <v>49.67</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>75</v>
       </c>
@@ -1956,8 +2577,27 @@
       <c r="G26" s="5">
         <v>2.9946999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <f t="shared" si="1"/>
+        <v>33.07</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>66</v>
       </c>
@@ -1979,8 +2619,27 @@
       <c r="G27" s="5">
         <v>6.5157999999999996</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <f t="shared" si="1"/>
+        <v>43.96</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
@@ -2002,8 +2661,27 @@
       <c r="G28" s="5">
         <v>7.0401999999999996</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <f t="shared" si="1"/>
+        <v>46.09</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
@@ -2025,8 +2703,27 @@
       <c r="G29" s="5">
         <v>20.5472</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>58.21</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M29" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N29">
+        <v>58.21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
@@ -2048,8 +2745,27 @@
       <c r="G30" s="5">
         <v>23.237500000000001</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>60.86</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M30" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N30">
+        <v>60.86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>54</v>
       </c>
@@ -2071,8 +2787,27 @@
       <c r="G31" s="5">
         <v>12.550700000000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <f t="shared" si="1"/>
+        <v>61.13</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
@@ -2094,8 +2829,27 @@
       <c r="G32" s="5">
         <v>4.2380000000000004</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <f t="shared" si="1"/>
+        <v>46.19</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -2117,8 +2871,27 @@
       <c r="G33" s="5">
         <v>4.4191000000000003</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <f t="shared" si="1"/>
+        <v>35.119999999999997</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>20</v>
       </c>
@@ -2140,8 +2913,27 @@
       <c r="G34" s="5">
         <v>18.1432</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="3"/>
+        <v>60.04</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M34" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N34">
+        <v>60.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>44</v>
       </c>
@@ -2163,8 +2955,27 @@
       <c r="G35" s="5">
         <v>15.417299999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="3"/>
+        <v>64.319999999999993</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M35" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N35">
+        <v>64.319999999999993</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>70</v>
       </c>
@@ -2186,8 +2997,27 @@
       <c r="G36" s="5">
         <v>15.570499999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="3"/>
+        <v>47.02</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M36" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N36">
+        <v>47.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
@@ -2209,8 +3039,27 @@
       <c r="G37" s="5">
         <v>6.2824</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <f t="shared" si="1"/>
+        <v>56.85</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -2232,8 +3081,27 @@
       <c r="G38" s="5">
         <v>7.7009999999999996</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <f t="shared" si="1"/>
+        <v>53.47</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>61</v>
       </c>
@@ -2255,8 +3123,27 @@
       <c r="G39" s="5">
         <v>43.774999999999999</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="3"/>
+        <v>61.3</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N39">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>7</v>
       </c>
@@ -2278,8 +3165,27 @@
       <c r="G40" s="5">
         <v>4.5247000000000002</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <f t="shared" si="1"/>
+        <v>47.41</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>22</v>
       </c>
@@ -2301,8 +3207,27 @@
       <c r="G41" s="5">
         <v>16.164200000000001</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="3"/>
+        <v>58.09</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M41" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N41">
+        <v>58.09</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>14</v>
       </c>
@@ -2324,8 +3249,27 @@
       <c r="G42" s="5">
         <v>11.299300000000001</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <f t="shared" si="1"/>
+        <v>34.71</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>27</v>
       </c>
@@ -2347,8 +3291,27 @@
       <c r="G43" s="5">
         <v>6.4661</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <f t="shared" si="1"/>
+        <v>51.64</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>42</v>
       </c>
@@ -2370,8 +3333,27 @@
       <c r="G44" s="5">
         <v>14.3863</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <f t="shared" si="1"/>
+        <v>58.03</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>59</v>
       </c>
@@ -2393,8 +3375,27 @@
       <c r="G45" s="5">
         <v>18.075199999999999</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="3"/>
+        <v>56.53</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M45" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N45">
+        <v>56.53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2416,8 +3417,27 @@
       <c r="G46" s="5">
         <v>8.5898000000000003</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <f t="shared" si="1"/>
+        <v>54.88</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>57</v>
       </c>
@@ -2439,8 +3459,27 @@
       <c r="G47" s="5">
         <v>5.3072999999999997</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <f t="shared" si="1"/>
+        <v>44.43</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>19</v>
       </c>
@@ -2462,8 +3501,27 @@
       <c r="G48" s="5">
         <v>24.271100000000001</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="3"/>
+        <v>69.98</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M48" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N48">
+        <v>69.98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2485,8 +3543,27 @@
       <c r="G49" s="5">
         <v>6.8183999999999996</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <f t="shared" si="1"/>
+        <v>51.14</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>17</v>
       </c>
@@ -2508,8 +3585,27 @@
       <c r="G50" s="5">
         <v>14.563700000000001</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <f t="shared" si="1"/>
+        <v>63.5</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>49</v>
       </c>
@@ -2531,8 +3627,27 @@
       <c r="G51" s="5">
         <v>2.2035999999999998</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <f t="shared" si="1"/>
+        <v>49.32</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>71</v>
       </c>
@@ -2554,8 +3669,27 @@
       <c r="G52" s="5">
         <v>32.428699999999999</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M52" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N52">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>47</v>
       </c>
@@ -2577,8 +3711,27 @@
       <c r="G53" s="5">
         <v>19.080300000000001</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="3"/>
+        <v>53.86</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M53" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N53">
+        <v>53.86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>24</v>
       </c>
@@ -2600,8 +3753,27 @@
       <c r="G54" s="5">
         <v>7.7512999999999996</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <f t="shared" si="1"/>
+        <v>48.92</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>28</v>
       </c>
@@ -2623,8 +3795,27 @@
       <c r="G55" s="5">
         <v>12.9817</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <f t="shared" si="1"/>
+        <v>62.62</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>45</v>
       </c>
@@ -2646,8 +3837,27 @@
       <c r="G56" s="5">
         <v>16.587599999999998</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="3"/>
+        <v>50.15</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N56">
+        <v>50.15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>48</v>
       </c>
@@ -2669,8 +3879,27 @@
       <c r="G57" s="5">
         <v>12.830500000000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <f t="shared" si="1"/>
+        <v>55.63</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>68</v>
       </c>
@@ -2692,8 +3921,27 @@
       <c r="G58" s="5">
         <v>24.767600000000002</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="3"/>
+        <v>48.72</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M58" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N58">
+        <v>48.72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>30</v>
       </c>
@@ -2715,8 +3963,27 @@
       <c r="G59" s="5">
         <v>30.696200000000001</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M59" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N59">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>46</v>
       </c>
@@ -2738,8 +4005,27 @@
       <c r="G60" s="5">
         <v>6.5964</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <f t="shared" si="1"/>
+        <v>44.34</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>62</v>
       </c>
@@ -2761,8 +4047,27 @@
       <c r="G61" s="5">
         <v>64.125100000000003</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="2"/>
+        <v>54.41</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>52</v>
       </c>
@@ -2784,8 +4089,27 @@
       <c r="G62" s="5">
         <v>10.0938</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <f t="shared" si="1"/>
+        <v>44.36</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>33</v>
       </c>
@@ -2807,8 +4131,27 @@
       <c r="G63" s="5">
         <v>18.5213</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="3"/>
+        <v>63.09</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M63" t="str">
+        <f t="shared" si="0"/>
+        <v>До 45</v>
+      </c>
+      <c r="N63">
+        <v>63.09</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>58</v>
       </c>
@@ -2830,8 +4173,27 @@
       <c r="G64" s="5">
         <v>11.868499999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <f t="shared" si="1"/>
+        <v>59.99</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>74</v>
       </c>
@@ -2853,8 +4215,27 @@
       <c r="G65" s="5">
         <v>11.0524</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <f t="shared" si="1"/>
+        <v>50.35</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>55</v>
       </c>
@@ -2876,8 +4257,27 @@
       <c r="G66" s="5">
         <v>84.392899999999997</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="2"/>
+        <v>74.42</v>
+      </c>
+      <c r="M66">
+        <f t="shared" ref="M66:M75" si="4">IF(J66&lt;&gt;0,$J$1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>23</v>
       </c>
@@ -2899,8 +4299,27 @@
       <c r="G67" s="5">
         <v>8.9933999999999994</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <f t="shared" ref="I67:I75" si="5">IF(G67 &lt; 15,D67, 0)</f>
+        <v>43.28</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K75" si="6">IF(G67&gt;45,D67, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>29</v>
       </c>
@@ -2922,8 +4341,27 @@
       <c r="G68" s="5">
         <v>10.960699999999999</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <f t="shared" si="5"/>
+        <v>59.3</v>
+      </c>
+      <c r="J68">
+        <f t="shared" ref="J68:J75" si="7">IF(AND(G68 &lt; 45, G68&gt;15),D68, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>10</v>
       </c>
@@ -2945,8 +4383,27 @@
       <c r="G69" s="5">
         <v>30.5215</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="7"/>
+        <v>60.16</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M69" t="str">
+        <f t="shared" si="4"/>
+        <v>До 45</v>
+      </c>
+      <c r="N69">
+        <v>60.16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>21</v>
       </c>
@@ -2968,8 +4425,27 @@
       <c r="G70" s="5">
         <v>10.133800000000001</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <f t="shared" si="5"/>
+        <v>47.45</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>3</v>
       </c>
@@ -2991,8 +4467,27 @@
       <c r="G71" s="5">
         <v>14.847200000000001</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <f t="shared" si="5"/>
+        <v>49.95</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>60</v>
       </c>
@@ -3014,8 +4509,27 @@
       <c r="G72" s="5">
         <v>14.7935</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <f t="shared" si="5"/>
+        <v>44.83</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3037,8 +4551,27 @@
       <c r="G73" s="5">
         <v>29.537600000000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="7"/>
+        <v>59.42</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M73" t="str">
+        <f t="shared" si="4"/>
+        <v>До 45</v>
+      </c>
+      <c r="N73">
+        <v>59.42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>9</v>
       </c>
@@ -3060,8 +4593,27 @@
       <c r="G74" s="5">
         <v>33.941499999999998</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="7"/>
+        <v>51.08</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M74" t="str">
+        <f t="shared" si="4"/>
+        <v>До 45</v>
+      </c>
+      <c r="N74">
+        <v>51.08</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>37</v>
       </c>
@@ -3083,36 +4635,55 @@
       <c r="G75" s="5">
         <v>7.3418999999999999</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <f t="shared" si="5"/>
+        <v>49.98</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -3333,12 +4904,26 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G148">
     <sortCondition ref="G2:G148"/>
   </sortState>
-  <conditionalFormatting sqref="G1 B1:F1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="G1 B1:F1048576 I1:K1">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>#N/A</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="#Н/Д">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="#Н/Д">
       <formula>NOT(ISERROR(SEARCH("#Н/Д",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G75">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
+      <formula>45</formula>
+      <formula>130</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>15</formula>
+      <formula>45</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+      <formula>0</formula>
+      <formula>15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5648,4 +7233,1121 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CC7A8BC-A545-4B05-86BC-2E171C8E3D06}">
+  <dimension ref="A2:B95"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B2" s="5">
+        <v>44.53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" s="5">
+        <v>50.57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="5">
+        <v>26.94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" s="5">
+        <v>61.54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="5">
+        <v>34.47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B7" s="5">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B8" s="5">
+        <v>32.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B9" s="5">
+        <v>42.66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B10" s="5">
+        <v>47.68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" s="5">
+        <v>43.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="5">
+        <v>49.76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" s="5">
+        <v>49.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" s="5">
+        <v>33.07</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" s="5">
+        <v>43.96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>305</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" s="5">
+        <v>61.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>305</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="5">
+        <v>35.119999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" s="5">
+        <v>56.85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>305</v>
+      </c>
+      <c r="B21" s="5">
+        <v>53.47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>305</v>
+      </c>
+      <c r="B22" s="5">
+        <v>47.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>305</v>
+      </c>
+      <c r="B23" s="5">
+        <v>34.71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>305</v>
+      </c>
+      <c r="B24" s="5">
+        <v>51.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>305</v>
+      </c>
+      <c r="B25" s="5">
+        <v>58.03</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>305</v>
+      </c>
+      <c r="B26" s="5">
+        <v>54.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>305</v>
+      </c>
+      <c r="B27" s="5">
+        <v>44.43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>305</v>
+      </c>
+      <c r="B28" s="5">
+        <v>51.14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B29" s="5">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>305</v>
+      </c>
+      <c r="B30" s="5">
+        <v>49.32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>305</v>
+      </c>
+      <c r="B31" s="5">
+        <v>48.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>305</v>
+      </c>
+      <c r="B32" s="5">
+        <v>62.62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>305</v>
+      </c>
+      <c r="B33" s="5">
+        <v>55.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>305</v>
+      </c>
+      <c r="B34" s="5">
+        <v>44.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>305</v>
+      </c>
+      <c r="B35" s="5">
+        <v>44.36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>305</v>
+      </c>
+      <c r="B36" s="5">
+        <v>59.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>305</v>
+      </c>
+      <c r="B37" s="5">
+        <v>50.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>305</v>
+      </c>
+      <c r="B38" s="5">
+        <v>43.28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>305</v>
+      </c>
+      <c r="B39" s="5">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>305</v>
+      </c>
+      <c r="B40" s="5">
+        <v>47.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>305</v>
+      </c>
+      <c r="B41" s="5">
+        <v>49.95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>305</v>
+      </c>
+      <c r="B42" s="5">
+        <v>44.83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>305</v>
+      </c>
+      <c r="B43" s="5">
+        <v>49.98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>306</v>
+      </c>
+      <c r="B44" s="5">
+        <v>73.319999999999993</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>306</v>
+      </c>
+      <c r="B45" s="5">
+        <v>56.74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>306</v>
+      </c>
+      <c r="B46" s="5">
+        <v>64.510000000000005</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>306</v>
+      </c>
+      <c r="B47" s="5">
+        <v>72.05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>306</v>
+      </c>
+      <c r="B48" s="5">
+        <v>54.28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>306</v>
+      </c>
+      <c r="B49" s="5">
+        <v>54.67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>306</v>
+      </c>
+      <c r="B50" s="5">
+        <v>60.22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>306</v>
+      </c>
+      <c r="B51" s="5">
+        <v>62.41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>306</v>
+      </c>
+      <c r="B52" s="5">
+        <v>51.44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>306</v>
+      </c>
+      <c r="B53" s="5">
+        <v>58.21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" s="5">
+        <v>60.86</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>306</v>
+      </c>
+      <c r="B75">
+        <v>60.04</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>306</v>
+      </c>
+      <c r="B76">
+        <v>64.319999999999993</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>306</v>
+      </c>
+      <c r="B77">
+        <v>47.02</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>306</v>
+      </c>
+      <c r="B78">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>306</v>
+      </c>
+      <c r="B79">
+        <v>58.09</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>306</v>
+      </c>
+      <c r="B80">
+        <v>56.53</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>306</v>
+      </c>
+      <c r="B81">
+        <v>69.98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>306</v>
+      </c>
+      <c r="B82">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>306</v>
+      </c>
+      <c r="B83">
+        <v>53.86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>306</v>
+      </c>
+      <c r="B84">
+        <v>50.15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>306</v>
+      </c>
+      <c r="B85">
+        <v>48.72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>306</v>
+      </c>
+      <c r="B86">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>306</v>
+      </c>
+      <c r="B87">
+        <v>63.09</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>306</v>
+      </c>
+      <c r="B88">
+        <v>60.16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>306</v>
+      </c>
+      <c r="B89">
+        <v>59.42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>306</v>
+      </c>
+      <c r="B90">
+        <v>51.08</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>307</v>
+      </c>
+      <c r="B91">
+        <v>61.06</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>307</v>
+      </c>
+      <c r="B92">
+        <v>63.78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>307</v>
+      </c>
+      <c r="B93">
+        <v>59.03</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>307</v>
+      </c>
+      <c r="B94">
+        <v>54.41</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>307</v>
+      </c>
+      <c r="B95">
+        <v>74.42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A347C7-FCB0-42E3-ADC8-A3CCF0557EEC}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" s="9">
+        <v>42</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2012.23</v>
+      </c>
+      <c r="D5" s="9">
+        <v>47.910238095238093</v>
+      </c>
+      <c r="E5" s="9">
+        <v>77.206343844366856</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B6" s="9">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1598.4699999999998</v>
+      </c>
+      <c r="D6" s="9">
+        <v>59.202592592592588</v>
+      </c>
+      <c r="E6" s="9">
+        <v>45.084089173790396</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" s="10">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10">
+        <v>312.7</v>
+      </c>
+      <c r="D7" s="10">
+        <v>62.54</v>
+      </c>
+      <c r="E7" s="10">
+        <v>55.81985000000077</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B12" s="9">
+        <v>2581.8180973759454</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1290.9090486879727</v>
+      </c>
+      <c r="E12" s="9">
+        <v>20.095600356522347</v>
+      </c>
+      <c r="F12" s="9">
+        <v>1.2138680148239023E-7</v>
+      </c>
+      <c r="G12" s="9">
+        <v>3.1257642368130321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B13" s="9">
+        <v>4560.9258161375665</v>
+      </c>
+      <c r="C13" s="9">
+        <v>71</v>
+      </c>
+      <c r="D13" s="9">
+        <v>64.238391776585445</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" s="10">
+        <v>7142.7439135135119</v>
+      </c>
+      <c r="C15" s="10">
+        <v>73</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23EFD91-DF1C-4765-933E-B2F19129394B}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>44.53</v>
+      </c>
+      <c r="B2">
+        <v>73.319999999999993</v>
+      </c>
+      <c r="C2">
+        <v>61.06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>50.57</v>
+      </c>
+      <c r="B3">
+        <v>56.74</v>
+      </c>
+      <c r="C3">
+        <v>63.78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>26.94</v>
+      </c>
+      <c r="B4">
+        <v>64.510000000000005</v>
+      </c>
+      <c r="C4">
+        <v>59.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>61.54</v>
+      </c>
+      <c r="B5">
+        <v>72.05</v>
+      </c>
+      <c r="C5">
+        <v>54.41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>34.47</v>
+      </c>
+      <c r="B6">
+        <v>54.28</v>
+      </c>
+      <c r="C6">
+        <v>74.42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>36.4</v>
+      </c>
+      <c r="B7">
+        <v>54.67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>32.68</v>
+      </c>
+      <c r="B8">
+        <v>60.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>42.66</v>
+      </c>
+      <c r="B9">
+        <v>62.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>47.68</v>
+      </c>
+      <c r="B10">
+        <v>51.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>43.39</v>
+      </c>
+      <c r="B11">
+        <v>58.21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>49.76</v>
+      </c>
+      <c r="B12">
+        <v>60.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>49.67</v>
+      </c>
+      <c r="B13">
+        <v>60.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>33.07</v>
+      </c>
+      <c r="B14">
+        <v>64.319999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>43.96</v>
+      </c>
+      <c r="B15">
+        <v>47.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>46.09</v>
+      </c>
+      <c r="B16">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>61.13</v>
+      </c>
+      <c r="B17">
+        <v>58.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>46.19</v>
+      </c>
+      <c r="B18">
+        <v>56.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>35.119999999999997</v>
+      </c>
+      <c r="B19">
+        <v>69.98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>56.85</v>
+      </c>
+      <c r="B20">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>53.47</v>
+      </c>
+      <c r="B21">
+        <v>53.86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>47.41</v>
+      </c>
+      <c r="B22">
+        <v>50.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>34.71</v>
+      </c>
+      <c r="B23">
+        <v>48.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>51.64</v>
+      </c>
+      <c r="B24">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>58.03</v>
+      </c>
+      <c r="B25">
+        <v>63.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>54.88</v>
+      </c>
+      <c r="B26">
+        <v>60.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>44.43</v>
+      </c>
+      <c r="B27">
+        <v>59.42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>51.14</v>
+      </c>
+      <c r="B28">
+        <v>51.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>49.32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>48.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>62.62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>55.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>44.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>44.36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>59.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>50.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>43.28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>47.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>49.95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>44.83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>49.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>